--- a/Result/profitability/2605.xlsx
+++ b/Result/profitability/2605.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.17</v>
       </c>
       <c r="M2" t="n">
-        <v>0.505</v>
+        <v>0.82875</v>
       </c>
       <c r="N2" t="n">
-        <v>31.01625</v>
+        <v>33.19374999999999</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,7 +681,7 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -690,7 +690,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>2.16</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7225</v>
+        <v>1.05625</v>
       </c>
       <c r="N3" t="n">
-        <v>36.06875</v>
+        <v>38.94625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -801,7 +801,7 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
         <v>1</v>
@@ -899,13 +899,13 @@
         <v>1.05</v>
       </c>
       <c r="M4" t="n">
-        <v>0.81125</v>
+        <v>1.185</v>
       </c>
       <c r="N4" t="n">
-        <v>40.765</v>
+        <v>46.0225</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,13 +1018,13 @@
         <v>0.89</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9200000000000002</v>
+        <v>1.27125</v>
       </c>
       <c r="N5" t="n">
-        <v>47.61</v>
+        <v>50.55374999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>1.14</v>
       </c>
       <c r="M6" t="n">
-        <v>1.0375</v>
+        <v>1.38</v>
       </c>
       <c r="N6" t="n">
-        <v>52.08750000000001</v>
+        <v>54.655</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>1.1</v>
       </c>
       <c r="M7" t="n">
-        <v>1.14125</v>
+        <v>1.3975</v>
       </c>
       <c r="N7" t="n">
-        <v>56.89375</v>
+        <v>56.825</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>2.46</v>
       </c>
       <c r="M8" t="n">
-        <v>1.32875</v>
+        <v>1.6225</v>
       </c>
       <c r="N8" t="n">
-        <v>58.69625</v>
+        <v>59.03</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2605</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1330</v>
+      </c>
+      <c r="D75" t="n">
+        <v>727</v>
+      </c>
+      <c r="E75" t="n">
+        <v>603</v>
+      </c>
+      <c r="F75" t="n">
+        <v>45.32</v>
+      </c>
+      <c r="G75" t="n">
+        <v>420</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>31.61%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1402</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1823</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1761</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="N75" t="n">
+        <v>29.23125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="X75" t="n">
+        <v>3.56060606060606</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.670000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.06260257913247358</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.081763895268718</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
